--- a/SKU_File_Mapping.xlsx
+++ b/SKU_File_Mapping.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TVS NIRIX Orbiter RVS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TVS NIRIX VCU Flashing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954C5596-480B-48BE-A71D-EAA056E8262F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81E1D9FC-7EDF-4403-BE4D-7F7BA6F908E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E20797B-847C-4FCF-A197-0E0654561CDB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9E20797B-847C-4FCF-A197-0E0654561CDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,20 +47,20 @@
     <t>Library</t>
   </si>
   <si>
-    <t>Orbiter_RVS.xlsx</t>
-  </si>
-  <si>
-    <t>KE190250,KE190990</t>
-  </si>
-  <si>
-    <t>Orbiter_RVS</t>
+    <t>NMB1190010GB,NMB1190010GB7P,NMB1190010GBBN,NMB1190010GBDN,NMB1190010GBFN,NMB1190010GBQN,NMB1190010GBSN,NMB1190010IN7P,NMB1190010INBN,NMB1190010INFN,NMB1190010INQN,NMB1190010UNFN,NMB1190020GB7P,NMB1190020GBBN,NMB1190020GBDN,NMB1190020GBFN,NMB1190020GBQN,NMB1190020GBSN,NMB1190030GBDN,NMB1190030GBFN,NMB1190030GBSN,NMB1190030INDN,NMB1190030INFN,NMB1190030INQN,NMB1190030INSN,NMB1190040GB,NMB1190040GBDN,NMB1190040GBFN,NMB1190040GBQN,NMB1190040GBSN,NMB1190040INDN,NMB1190040INFN,NMB1190040INQN,NMB1190040INSN,NMB1190050GBBN,NMB1190050GBDN,NMB1190050GBQN,NMB1190050GBSN,NMB1190050IN7P,NMB1190050USDN,NMB1190060GBBN,NMB1190060IN7P,NMB1190060USFN,NMB1190070AUDN,NMB1190070GBDN,NMB1190070GBQN,NMB1190070GBSN,NMB1190070INSN,NMB1190080GBDN,NMB1190080GBFN,NMB1190080GBQN,NMB1190080GBSN,NMB1190080INDN</t>
+  </si>
+  <si>
+    <t>B110_Cluster_Flashing.xlsx</t>
+  </si>
+  <si>
+    <t>B110_Cluster_Flashing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,15 +69,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -85,12 +91,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,32 +449,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1CC9904-5AC1-4F43-857A-3A029873D0C5}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
